--- a/artfynd/S 1051-2022 artfynd.xlsx
+++ b/artfynd/S 1051-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75220485</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75238260</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73070777</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071417</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071645</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071291</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071306</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071446</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1682,6 +1727,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071316</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1795,6 +1845,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071002</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1908,6 +1963,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071136</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2018,6 +2078,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071579</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2124,6 +2189,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79714209</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2230,6 +2300,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79714307</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2341,6 +2416,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79714372</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2446,6 +2526,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73070893</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2559,6 +2644,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73070998</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2672,6 +2762,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071060</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2777,6 +2872,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071352</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2882,6 +2982,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071479</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2988,6 +3093,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79714277</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3094,6 +3204,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79714323</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3207,6 +3322,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73070875</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3312,6 +3432,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73070914</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3417,6 +3542,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73070923</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3522,6 +3652,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73070947</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3627,6 +3762,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73070978</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3740,6 +3880,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071102</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3853,6 +3998,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071156</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3966,6 +4116,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071169</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4071,6 +4226,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071272</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4184,6 +4344,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071296</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4297,6 +4462,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071342</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4408,6 +4578,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79714223</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4513,6 +4688,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73070871</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4618,6 +4798,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73070928</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4723,6 +4908,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071363</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4828,6 +5018,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071617</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4938,6 +5133,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071430</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5048,6 +5248,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74567462</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5153,6 +5358,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73070869</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5258,6 +5468,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73070982</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5363,6 +5578,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071006</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5468,6 +5688,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071696</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5573,6 +5798,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071130</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5686,6 +5916,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071152</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5791,6 +6026,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071463</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5896,6 +6136,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73071573</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5993,6 +6238,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75238258</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6103,6 +6353,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74563802</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6205,6 +6460,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72702933</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6302,6 +6562,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75238262</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6417,8 +6682,68 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79714346</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>